--- a/validation/expert_reviews/E1_extraction_review.xlsx
+++ b/validation/expert_reviews/E1_extraction_review.xlsx
@@ -580,7 +580,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Review workbook — Florian</t>
+          <t>Review workbook — E1</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E1    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Florian</t>
+          <t>Rating — E1</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E1    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Florian</t>
+          <t>Rating — E1</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E1    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Florian</t>
+          <t>Rating — E1</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E1    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Florian</t>
+          <t>Rating — E1</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E1    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Florian</t>
+          <t>Rating — E1</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E1    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Florian</t>
+          <t>Rating — E1</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E1    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4331,6 +4331,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4446,6 +4447,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -4788,7 +4790,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E1    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4848,6 +4850,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4963,6 +4966,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5305,7 +5309,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E1    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5365,6 +5369,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5480,6 +5485,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5822,7 +5828,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E1    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5882,6 +5888,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5997,6 +6004,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6339,7 +6347,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E1    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -6399,6 +6407,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -6514,6 +6523,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6856,7 +6866,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E1    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -6916,6 +6926,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -7031,6 +7042,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -7373,7 +7385,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E1    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -7433,6 +7445,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -7548,6 +7561,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -7895,7 +7909,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Florian    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E1    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7928,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Florian</t>
+          <t>Rating — E1</t>
         </is>
       </c>
     </row>
